--- a/ipar40tk-server/simulator/baselines/high-rpm_high-stress_filled_simulator.xlsx
+++ b/ipar40tk-server/simulator/baselines/high-rpm_high-stress_filled_simulator.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bprof2025\COMPACT-MAPS\COMPACT-MAPS\ipar40tk-server\simulator\baselines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COMPACT-MAPS\COMPACT-MAPS\ipar40tk-server\simulator\baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C5B2D6-90BD-4750-8D94-5A09864D7E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5D50F922-5467-48FE-811E-3D65261385B3}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4511,8 +4510,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4877,11 +4876,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2551C2-3D39-4BF2-9351-B2AA36549EA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F529"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4901,7 +4900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -4921,7 +4920,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -4941,7 +4940,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4961,7 +4960,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4981,7 +4980,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -5001,7 +5000,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -5021,7 +5020,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -5041,7 +5040,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -5061,7 +5060,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -5081,7 +5080,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -5101,7 +5100,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -5121,7 +5120,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -5141,7 +5140,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -5161,7 +5160,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -5181,7 +5180,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -5201,7 +5200,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -5221,7 +5220,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -5241,7 +5240,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -5261,7 +5260,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -5281,7 +5280,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -5301,7 +5300,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -5321,7 +5320,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -5329,7 +5328,7 @@
         <v>1335.36</v>
       </c>
       <c r="C23">
-        <v>-100</v>
+        <v>42.13</v>
       </c>
       <c r="D23" t="s">
         <v>296</v>
@@ -5341,7 +5340,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -5361,7 +5360,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -5381,7 +5380,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -5401,7 +5400,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -5421,7 +5420,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -5441,7 +5440,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -5461,7 +5460,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -5481,7 +5480,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -5501,7 +5500,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -5521,7 +5520,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -5541,7 +5540,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -5561,7 +5560,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -5581,7 +5580,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -5601,7 +5600,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -5621,7 +5620,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -5641,7 +5640,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -5661,7 +5660,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -5681,7 +5680,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -5701,7 +5700,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -5721,7 +5720,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -5741,7 +5740,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -5761,7 +5760,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -5781,7 +5780,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -5801,7 +5800,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -5821,7 +5820,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -5841,7 +5840,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -5861,7 +5860,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -5881,7 +5880,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -5901,7 +5900,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -5921,7 +5920,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -5941,7 +5940,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -5961,7 +5960,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -5981,7 +5980,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -6001,7 +6000,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -6021,7 +6020,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -6041,7 +6040,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -6061,7 +6060,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -6081,7 +6080,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -6089,7 +6088,7 @@
         <v>1324.75</v>
       </c>
       <c r="C61">
-        <v>-100</v>
+        <v>41.72</v>
       </c>
       <c r="D61" t="s">
         <v>321</v>
@@ -6101,7 +6100,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -6121,7 +6120,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -6141,7 +6140,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -6161,7 +6160,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -6181,7 +6180,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -6201,7 +6200,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -6221,7 +6220,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -6241,7 +6240,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -6261,7 +6260,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -6281,7 +6280,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -6301,7 +6300,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -6321,7 +6320,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -6341,7 +6340,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -6361,7 +6360,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -6381,7 +6380,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -6401,7 +6400,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -6421,7 +6420,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -6441,7 +6440,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -6461,7 +6460,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -6481,7 +6480,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>85</v>
       </c>
@@ -6501,7 +6500,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -6521,7 +6520,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -6541,7 +6540,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>88</v>
       </c>
@@ -6561,7 +6560,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -6581,7 +6580,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>90</v>
       </c>
@@ -6601,7 +6600,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -6621,7 +6620,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -6641,7 +6640,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>93</v>
       </c>
@@ -6661,7 +6660,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -6681,7 +6680,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -6701,7 +6700,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -6721,7 +6720,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -6741,7 +6740,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -6761,7 +6760,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -6781,7 +6780,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>100</v>
       </c>
@@ -6801,7 +6800,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>101</v>
       </c>
@@ -6821,7 +6820,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>102</v>
       </c>
@@ -6841,7 +6840,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -6861,7 +6860,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -6881,7 +6880,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -6901,7 +6900,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -6921,7 +6920,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -6941,7 +6940,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>108</v>
       </c>
@@ -6961,7 +6960,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -6981,7 +6980,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>110</v>
       </c>
@@ -7001,7 +7000,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -7021,7 +7020,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -7041,7 +7040,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -7061,7 +7060,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -7081,7 +7080,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -7101,7 +7100,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -7121,7 +7120,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>117</v>
       </c>
@@ -7141,7 +7140,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>118</v>
       </c>
@@ -7161,7 +7160,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>119</v>
       </c>
@@ -7181,7 +7180,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>120</v>
       </c>
@@ -7201,7 +7200,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>121</v>
       </c>
@@ -7221,7 +7220,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>122</v>
       </c>
@@ -7241,7 +7240,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>101</v>
       </c>
@@ -7261,7 +7260,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>123</v>
       </c>
@@ -7281,7 +7280,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>124</v>
       </c>
@@ -7301,7 +7300,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>125</v>
       </c>
@@ -7321,7 +7320,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>126</v>
       </c>
@@ -7341,7 +7340,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>127</v>
       </c>
@@ -7361,7 +7360,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>128</v>
       </c>
@@ -7381,7 +7380,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>129</v>
       </c>
@@ -7401,7 +7400,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>130</v>
       </c>
@@ -7421,7 +7420,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>131</v>
       </c>
@@ -7441,7 +7440,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>132</v>
       </c>
@@ -7461,7 +7460,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>133</v>
       </c>
@@ -7481,7 +7480,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>134</v>
       </c>
@@ -7501,7 +7500,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>135</v>
       </c>
@@ -7521,7 +7520,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>136</v>
       </c>
@@ -7541,7 +7540,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>137</v>
       </c>
@@ -7561,7 +7560,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>138</v>
       </c>
@@ -7581,7 +7580,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>139</v>
       </c>
@@ -7601,7 +7600,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>140</v>
       </c>
@@ -7621,7 +7620,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>141</v>
       </c>
@@ -7641,7 +7640,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>142</v>
       </c>
@@ -7661,7 +7660,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>143</v>
       </c>
@@ -7681,7 +7680,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>144</v>
       </c>
@@ -7701,7 +7700,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>145</v>
       </c>
@@ -7721,7 +7720,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>146</v>
       </c>
@@ -7741,7 +7740,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>147</v>
       </c>
@@ -7761,7 +7760,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>148</v>
       </c>
@@ -7781,7 +7780,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>149</v>
       </c>
@@ -7801,7 +7800,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>150</v>
       </c>
@@ -7821,7 +7820,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>151</v>
       </c>
@@ -7841,7 +7840,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>152</v>
       </c>
@@ -7861,7 +7860,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>153</v>
       </c>
@@ -7881,7 +7880,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>154</v>
       </c>
@@ -7901,7 +7900,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>155</v>
       </c>
@@ -7921,7 +7920,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>156</v>
       </c>
@@ -7941,7 +7940,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>157</v>
       </c>
@@ -7961,7 +7960,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>158</v>
       </c>
@@ -7981,7 +7980,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>159</v>
       </c>
@@ -8001,7 +8000,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>160</v>
       </c>
@@ -8021,7 +8020,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>161</v>
       </c>
@@ -8041,7 +8040,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>162</v>
       </c>
@@ -8061,7 +8060,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>163</v>
       </c>
@@ -8081,7 +8080,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>164</v>
       </c>
@@ -8101,7 +8100,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>165</v>
       </c>
@@ -8121,7 +8120,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>166</v>
       </c>
@@ -8141,7 +8140,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>167</v>
       </c>
@@ -8161,7 +8160,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>168</v>
       </c>
@@ -8181,7 +8180,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>169</v>
       </c>
@@ -8201,7 +8200,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>170</v>
       </c>
@@ -8221,7 +8220,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>171</v>
       </c>
@@ -8241,7 +8240,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>172</v>
       </c>
@@ -8261,7 +8260,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>173</v>
       </c>
@@ -8281,7 +8280,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>174</v>
       </c>
@@ -8301,7 +8300,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>175</v>
       </c>
@@ -8321,7 +8320,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>176</v>
       </c>
@@ -8341,7 +8340,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>177</v>
       </c>
@@ -8361,7 +8360,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>178</v>
       </c>
@@ -8381,7 +8380,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>179</v>
       </c>
@@ -8401,7 +8400,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>180</v>
       </c>
@@ -8421,7 +8420,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>181</v>
       </c>
@@ -8441,7 +8440,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>182</v>
       </c>
@@ -8461,7 +8460,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>183</v>
       </c>
@@ -8481,7 +8480,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>184</v>
       </c>
@@ -8501,7 +8500,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>185</v>
       </c>
@@ -8521,7 +8520,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>186</v>
       </c>
@@ -8541,7 +8540,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>187</v>
       </c>
@@ -8561,7 +8560,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>188</v>
       </c>
@@ -8581,7 +8580,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
         <v>189</v>
       </c>
@@ -8601,7 +8600,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
         <v>190</v>
       </c>
@@ -8621,7 +8620,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
         <v>191</v>
       </c>
@@ -8641,7 +8640,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>192</v>
       </c>
@@ -8661,7 +8660,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>193</v>
       </c>
@@ -8681,7 +8680,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>194</v>
       </c>
@@ -8701,7 +8700,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>195</v>
       </c>
@@ -8721,7 +8720,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>196</v>
       </c>
@@ -8741,7 +8740,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>197</v>
       </c>
@@ -8761,7 +8760,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>198</v>
       </c>
@@ -8781,7 +8780,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>199</v>
       </c>
@@ -8801,7 +8800,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>200</v>
       </c>
@@ -8821,7 +8820,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>201</v>
       </c>
@@ -8841,7 +8840,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>202</v>
       </c>
@@ -8861,7 +8860,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>203</v>
       </c>
@@ -8881,7 +8880,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>204</v>
       </c>
@@ -8901,7 +8900,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>205</v>
       </c>
@@ -8921,7 +8920,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>206</v>
       </c>
@@ -8941,7 +8940,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>207</v>
       </c>
@@ -8961,7 +8960,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>208</v>
       </c>
@@ -8981,7 +8980,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>209</v>
       </c>
@@ -9001,7 +9000,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>210</v>
       </c>
@@ -9021,7 +9020,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>211</v>
       </c>
@@ -9041,7 +9040,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>212</v>
       </c>
@@ -9061,7 +9060,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>213</v>
       </c>
@@ -9081,7 +9080,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>214</v>
       </c>
@@ -9101,7 +9100,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6">
       <c r="A212" t="s">
         <v>215</v>
       </c>
@@ -9121,7 +9120,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>216</v>
       </c>
@@ -9141,7 +9140,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6">
       <c r="A214" t="s">
         <v>217</v>
       </c>
@@ -9161,7 +9160,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6">
       <c r="A215" t="s">
         <v>218</v>
       </c>
@@ -9181,7 +9180,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>219</v>
       </c>
@@ -9201,7 +9200,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>220</v>
       </c>
@@ -9221,7 +9220,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>221</v>
       </c>
@@ -9241,7 +9240,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6">
       <c r="A219" t="s">
         <v>222</v>
       </c>
@@ -9261,7 +9260,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6">
       <c r="A220" t="s">
         <v>223</v>
       </c>
@@ -9281,7 +9280,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6">
       <c r="A221" t="s">
         <v>224</v>
       </c>
@@ -9301,7 +9300,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6">
       <c r="A222" t="s">
         <v>225</v>
       </c>
@@ -9321,7 +9320,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>226</v>
       </c>
@@ -9341,7 +9340,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6">
       <c r="A224" t="s">
         <v>227</v>
       </c>
@@ -9361,7 +9360,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6">
       <c r="A225" t="s">
         <v>228</v>
       </c>
@@ -9381,7 +9380,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6">
       <c r="A226" t="s">
         <v>229</v>
       </c>
@@ -9401,7 +9400,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6">
       <c r="A227" t="s">
         <v>230</v>
       </c>
@@ -9421,7 +9420,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>231</v>
       </c>
@@ -9441,7 +9440,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6">
       <c r="A229" t="s">
         <v>232</v>
       </c>
@@ -9461,7 +9460,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6">
       <c r="A230" t="s">
         <v>233</v>
       </c>
@@ -9481,7 +9480,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6">
       <c r="A231" t="s">
         <v>234</v>
       </c>
@@ -9501,7 +9500,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6">
       <c r="A232" t="s">
         <v>235</v>
       </c>
@@ -9521,7 +9520,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6">
       <c r="A233" t="s">
         <v>236</v>
       </c>
@@ -9541,7 +9540,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6">
       <c r="A234" t="s">
         <v>237</v>
       </c>
@@ -9561,7 +9560,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6">
       <c r="A235" t="s">
         <v>238</v>
       </c>
@@ -9581,7 +9580,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6">
       <c r="A236" t="s">
         <v>239</v>
       </c>
@@ -9601,7 +9600,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6">
       <c r="A237" t="s">
         <v>240</v>
       </c>
@@ -9621,7 +9620,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6">
       <c r="A238" t="s">
         <v>241</v>
       </c>
@@ -9641,7 +9640,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6">
       <c r="A239" t="s">
         <v>242</v>
       </c>
@@ -9661,7 +9660,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6">
       <c r="A240" t="s">
         <v>243</v>
       </c>
@@ -9681,7 +9680,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6">
       <c r="A241" t="s">
         <v>244</v>
       </c>
@@ -9701,7 +9700,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6">
       <c r="A242" t="s">
         <v>245</v>
       </c>
@@ -9721,7 +9720,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6">
       <c r="A243" t="s">
         <v>246</v>
       </c>
@@ -9741,7 +9740,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6">
       <c r="A244" t="s">
         <v>247</v>
       </c>
@@ -9761,7 +9760,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6">
       <c r="A245" t="s">
         <v>248</v>
       </c>
@@ -9781,7 +9780,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6">
       <c r="A246" t="s">
         <v>249</v>
       </c>
@@ -9801,7 +9800,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6">
       <c r="A247" t="s">
         <v>250</v>
       </c>
@@ -9821,7 +9820,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6">
       <c r="A248" t="s">
         <v>251</v>
       </c>
@@ -9841,7 +9840,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6">
       <c r="A249" t="s">
         <v>252</v>
       </c>
@@ -9861,7 +9860,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6">
       <c r="A250" t="s">
         <v>253</v>
       </c>
@@ -9881,7 +9880,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6">
       <c r="A251" t="s">
         <v>254</v>
       </c>
@@ -9901,7 +9900,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6">
       <c r="A252" t="s">
         <v>255</v>
       </c>
@@ -9921,7 +9920,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6">
       <c r="A253" t="s">
         <v>256</v>
       </c>
@@ -9941,7 +9940,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6">
       <c r="A254" t="s">
         <v>257</v>
       </c>
@@ -9961,7 +9960,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6">
       <c r="A255" t="s">
         <v>258</v>
       </c>
@@ -9981,7 +9980,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6">
       <c r="A256" t="s">
         <v>259</v>
       </c>
@@ -10001,7 +10000,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>260</v>
       </c>
@@ -10021,7 +10020,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>261</v>
       </c>
@@ -10041,7 +10040,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>262</v>
       </c>
@@ -10061,7 +10060,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>263</v>
       </c>
@@ -10081,7 +10080,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>264</v>
       </c>
@@ -10101,7 +10100,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>265</v>
       </c>
@@ -10121,7 +10120,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>266</v>
       </c>
@@ -10141,7 +10140,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>267</v>
       </c>
@@ -10161,7 +10160,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>268</v>
       </c>
@@ -10181,7 +10180,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>269</v>
       </c>
@@ -10201,7 +10200,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>270</v>
       </c>
@@ -10221,7 +10220,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>271</v>
       </c>
@@ -10241,7 +10240,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>272</v>
       </c>
@@ -10261,7 +10260,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>273</v>
       </c>
@@ -10281,7 +10280,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>274</v>
       </c>
@@ -10301,7 +10300,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>275</v>
       </c>
@@ -10321,7 +10320,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>276</v>
       </c>
@@ -10341,7 +10340,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>277</v>
       </c>
@@ -10361,7 +10360,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>278</v>
       </c>
@@ -10381,7 +10380,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>279</v>
       </c>
@@ -10401,7 +10400,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>280</v>
       </c>
@@ -10421,7 +10420,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>281</v>
       </c>
@@ -10441,7 +10440,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>282</v>
       </c>
@@ -10461,7 +10460,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6">
       <c r="D280" t="s">
         <v>505</v>
       </c>
@@ -10472,7 +10471,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6">
       <c r="D281" t="s">
         <v>506</v>
       </c>
@@ -10483,7 +10482,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6">
       <c r="D282" t="s">
         <v>507</v>
       </c>
@@ -10494,7 +10493,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6">
       <c r="D283" t="s">
         <v>500</v>
       </c>
@@ -10505,7 +10504,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6">
       <c r="D284" t="s">
         <v>501</v>
       </c>
@@ -10516,7 +10515,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6">
       <c r="D285" t="s">
         <v>502</v>
       </c>
@@ -10527,7 +10526,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6">
       <c r="D286" t="s">
         <v>503</v>
       </c>
@@ -10538,7 +10537,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6">
       <c r="D287" t="s">
         <v>504</v>
       </c>
@@ -10549,7 +10548,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6">
       <c r="D288" t="s">
         <v>505</v>
       </c>
@@ -10560,7 +10559,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="289" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="4:6">
       <c r="D289" t="s">
         <v>506</v>
       </c>
@@ -10571,7 +10570,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="290" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="4:6">
       <c r="D290" t="s">
         <v>508</v>
       </c>
@@ -10582,7 +10581,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="291" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="4:6">
       <c r="D291" t="s">
         <v>509</v>
       </c>
@@ -10593,7 +10592,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="292" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="4:6">
       <c r="D292" t="s">
         <v>510</v>
       </c>
@@ -10604,7 +10603,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="293" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="4:6">
       <c r="D293" t="s">
         <v>511</v>
       </c>
@@ -10615,7 +10614,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="294" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="4:6">
       <c r="D294" t="s">
         <v>512</v>
       </c>
@@ -10626,7 +10625,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="295" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="4:6">
       <c r="D295" t="s">
         <v>513</v>
       </c>
@@ -10637,7 +10636,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="296" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="4:6">
       <c r="D296" t="s">
         <v>514</v>
       </c>
@@ -10648,7 +10647,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="297" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="4:6">
       <c r="D297" t="s">
         <v>515</v>
       </c>
@@ -10659,7 +10658,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="298" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="4:6">
       <c r="D298" t="s">
         <v>516</v>
       </c>
@@ -10670,7 +10669,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="299" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="4:6">
       <c r="D299" t="s">
         <v>509</v>
       </c>
@@ -10681,7 +10680,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="300" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="4:6">
       <c r="D300" t="s">
         <v>510</v>
       </c>
@@ -10692,7 +10691,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="301" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="4:6">
       <c r="D301" t="s">
         <v>511</v>
       </c>
@@ -10703,7 +10702,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="302" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="4:6">
       <c r="D302" t="s">
         <v>512</v>
       </c>
@@ -10714,7 +10713,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="303" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="4:6">
       <c r="D303" t="s">
         <v>513</v>
       </c>
@@ -10725,7 +10724,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="304" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="4:6">
       <c r="D304" t="s">
         <v>514</v>
       </c>
@@ -10736,7 +10735,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="305" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="4:6">
       <c r="D305" t="s">
         <v>515</v>
       </c>
@@ -10747,7 +10746,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="306" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="4:6">
       <c r="D306" t="s">
         <v>517</v>
       </c>
@@ -10758,7 +10757,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="307" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="4:6">
       <c r="D307" t="s">
         <v>518</v>
       </c>
@@ -10769,7 +10768,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="308" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="4:6">
       <c r="D308" t="s">
         <v>519</v>
       </c>
@@ -10780,7 +10779,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="309" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="4:6">
       <c r="D309" t="s">
         <v>520</v>
       </c>
@@ -10791,7 +10790,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="310" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="4:6">
       <c r="D310" t="s">
         <v>521</v>
       </c>
@@ -10802,7 +10801,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="311" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="4:6">
       <c r="D311" t="s">
         <v>522</v>
       </c>
@@ -10813,7 +10812,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="312" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="4:6">
       <c r="D312" t="s">
         <v>523</v>
       </c>
@@ -10824,7 +10823,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="313" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="4:6">
       <c r="D313" t="s">
         <v>524</v>
       </c>
@@ -10835,7 +10834,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="314" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="4:6">
       <c r="D314" t="s">
         <v>525</v>
       </c>
@@ -10846,7 +10845,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="315" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="4:6">
       <c r="D315" t="s">
         <v>526</v>
       </c>
@@ -10857,7 +10856,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="316" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="4:6">
       <c r="D316" t="s">
         <v>527</v>
       </c>
@@ -10868,7 +10867,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="317" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="4:6">
       <c r="D317" t="s">
         <v>528</v>
       </c>
@@ -10879,7 +10878,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="318" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="4:6">
       <c r="D318" t="s">
         <v>529</v>
       </c>
@@ -10890,7 +10889,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="319" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="4:6">
       <c r="D319" t="s">
         <v>530</v>
       </c>
@@ -10901,7 +10900,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="320" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="4:6">
       <c r="D320" t="s">
         <v>531</v>
       </c>
@@ -10912,7 +10911,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="321" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="4:6">
       <c r="D321" t="s">
         <v>532</v>
       </c>
@@ -10923,7 +10922,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="322" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="4:6">
       <c r="D322" t="s">
         <v>533</v>
       </c>
@@ -10934,7 +10933,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="323" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="4:6">
       <c r="D323" t="s">
         <v>526</v>
       </c>
@@ -10945,7 +10944,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="324" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="4:6">
       <c r="D324" t="s">
         <v>527</v>
       </c>
@@ -10956,7 +10955,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="325" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="4:6">
       <c r="D325" t="s">
         <v>528</v>
       </c>
@@ -10967,7 +10966,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="326" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="4:6">
       <c r="D326" t="s">
         <v>529</v>
       </c>
@@ -10978,7 +10977,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="327" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="4:6">
       <c r="D327" t="s">
         <v>530</v>
       </c>
@@ -10989,7 +10988,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="328" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="4:6">
       <c r="D328" t="s">
         <v>531</v>
       </c>
@@ -11000,7 +10999,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="329" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="4:6">
       <c r="D329" t="s">
         <v>532</v>
       </c>
@@ -11011,7 +11010,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="330" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="4:6">
       <c r="D330" t="s">
         <v>534</v>
       </c>
@@ -11022,7 +11021,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="331" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="4:6">
       <c r="D331" t="s">
         <v>535</v>
       </c>
@@ -11033,7 +11032,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="332" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="4:6">
       <c r="D332" t="s">
         <v>536</v>
       </c>
@@ -11044,7 +11043,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="333" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="4:6">
       <c r="D333" t="s">
         <v>537</v>
       </c>
@@ -11055,7 +11054,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="334" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="4:6">
       <c r="D334" t="s">
         <v>538</v>
       </c>
@@ -11066,7 +11065,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="335" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="4:6">
       <c r="D335" t="s">
         <v>539</v>
       </c>
@@ -11077,7 +11076,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="336" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="4:6">
       <c r="D336" t="s">
         <v>540</v>
       </c>
@@ -11088,7 +11087,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="337" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="4:6">
       <c r="D337" t="s">
         <v>541</v>
       </c>
@@ -11099,7 +11098,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="338" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="4:6">
       <c r="D338" t="s">
         <v>542</v>
       </c>
@@ -11110,7 +11109,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="339" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="4:6">
       <c r="D339" t="s">
         <v>535</v>
       </c>
@@ -11121,7 +11120,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="340" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="4:6">
       <c r="D340" t="s">
         <v>536</v>
       </c>
@@ -11132,7 +11131,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="341" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="4:6">
       <c r="D341" t="s">
         <v>537</v>
       </c>
@@ -11143,7 +11142,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="342" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="4:6">
       <c r="D342" t="s">
         <v>538</v>
       </c>
@@ -11154,7 +11153,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="343" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="4:6">
       <c r="D343" t="s">
         <v>539</v>
       </c>
@@ -11165,7 +11164,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="344" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="4:6">
       <c r="D344" t="s">
         <v>540</v>
       </c>
@@ -11176,7 +11175,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="345" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="4:6">
       <c r="D345" t="s">
         <v>541</v>
       </c>
@@ -11187,7 +11186,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="346" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="4:6">
       <c r="D346" t="s">
         <v>543</v>
       </c>
@@ -11198,7 +11197,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="347" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="4:6">
       <c r="D347" t="s">
         <v>544</v>
       </c>
@@ -11209,7 +11208,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="348" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="4:6">
       <c r="D348" t="s">
         <v>545</v>
       </c>
@@ -11220,7 +11219,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="349" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="4:6">
       <c r="D349" t="s">
         <v>546</v>
       </c>
@@ -11231,7 +11230,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="350" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="4:6">
       <c r="D350" t="s">
         <v>547</v>
       </c>
@@ -11242,7 +11241,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="351" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="4:6">
       <c r="D351" t="s">
         <v>548</v>
       </c>
@@ -11253,7 +11252,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="352" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="4:6">
       <c r="D352" t="s">
         <v>549</v>
       </c>
@@ -11264,7 +11263,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="353" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="353" spans="4:6">
       <c r="D353" t="s">
         <v>550</v>
       </c>
@@ -11275,7 +11274,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="354" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="4:6">
       <c r="D354" t="s">
         <v>551</v>
       </c>
@@ -11286,7 +11285,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="355" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="4:6">
       <c r="D355" t="s">
         <v>544</v>
       </c>
@@ -11297,7 +11296,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="356" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="4:6">
       <c r="D356" t="s">
         <v>545</v>
       </c>
@@ -11308,7 +11307,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="357" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="4:6">
       <c r="D357" t="s">
         <v>546</v>
       </c>
@@ -11319,7 +11318,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="358" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="4:6">
       <c r="D358" t="s">
         <v>547</v>
       </c>
@@ -11330,7 +11329,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="359" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="4:6">
       <c r="D359" t="s">
         <v>548</v>
       </c>
@@ -11341,7 +11340,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="360" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="4:6">
       <c r="D360" t="s">
         <v>549</v>
       </c>
@@ -11352,7 +11351,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="361" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="4:6">
       <c r="D361" t="s">
         <v>550</v>
       </c>
@@ -11363,7 +11362,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="362" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="4:6">
       <c r="D362" t="s">
         <v>552</v>
       </c>
@@ -11374,7 +11373,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="363" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="363" spans="4:6">
       <c r="D363" t="s">
         <v>553</v>
       </c>
@@ -11385,7 +11384,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="364" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="4:6">
       <c r="D364" t="s">
         <v>554</v>
       </c>
@@ -11396,7 +11395,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="365" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="4:6">
       <c r="D365" t="s">
         <v>555</v>
       </c>
@@ -11407,7 +11406,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="366" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="4:6">
       <c r="D366" t="s">
         <v>556</v>
       </c>
@@ -11418,7 +11417,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="367" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="4:6">
       <c r="D367" t="s">
         <v>557</v>
       </c>
@@ -11429,7 +11428,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="368" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="4:6">
       <c r="D368" t="s">
         <v>558</v>
       </c>
@@ -11440,7 +11439,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="369" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="4:6">
       <c r="D369" t="s">
         <v>559</v>
       </c>
@@ -11451,7 +11450,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="370" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="4:6">
       <c r="D370" t="s">
         <v>560</v>
       </c>
@@ -11462,7 +11461,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="371" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="4:6">
       <c r="D371" t="s">
         <v>553</v>
       </c>
@@ -11473,7 +11472,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="372" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="4:6">
       <c r="D372" t="s">
         <v>554</v>
       </c>
@@ -11484,7 +11483,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="373" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="4:6">
       <c r="D373" t="s">
         <v>555</v>
       </c>
@@ -11495,7 +11494,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="374" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="4:6">
       <c r="D374" t="s">
         <v>556</v>
       </c>
@@ -11506,7 +11505,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="375" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="4:6">
       <c r="D375" t="s">
         <v>557</v>
       </c>
@@ -11517,7 +11516,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="376" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="4:6">
       <c r="D376" t="s">
         <v>558</v>
       </c>
@@ -11528,7 +11527,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="377" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="4:6">
       <c r="D377" t="s">
         <v>559</v>
       </c>
@@ -11539,7 +11538,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="378" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="4:6">
       <c r="D378" t="s">
         <v>561</v>
       </c>
@@ -11550,7 +11549,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="379" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="4:6">
       <c r="D379" t="s">
         <v>562</v>
       </c>
@@ -11561,7 +11560,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="380" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="4:6">
       <c r="D380" t="s">
         <v>563</v>
       </c>
@@ -11572,7 +11571,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="381" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="4:6">
       <c r="D381" t="s">
         <v>564</v>
       </c>
@@ -11583,7 +11582,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="382" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="4:6">
       <c r="D382" t="s">
         <v>565</v>
       </c>
@@ -11594,7 +11593,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="383" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="4:6">
       <c r="D383" t="s">
         <v>566</v>
       </c>
@@ -11605,7 +11604,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="384" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="4:6">
       <c r="D384" t="s">
         <v>567</v>
       </c>
@@ -11616,7 +11615,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="385" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="4:6">
       <c r="D385" t="s">
         <v>568</v>
       </c>
@@ -11627,7 +11626,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="386" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="4:6">
       <c r="D386" t="s">
         <v>569</v>
       </c>
@@ -11638,7 +11637,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="387" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="4:6">
       <c r="D387" t="s">
         <v>562</v>
       </c>
@@ -11649,7 +11648,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="388" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="4:6">
       <c r="D388" t="s">
         <v>563</v>
       </c>
@@ -11660,7 +11659,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="389" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="4:6">
       <c r="D389" t="s">
         <v>564</v>
       </c>
@@ -11671,7 +11670,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="390" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="4:6">
       <c r="D390" t="s">
         <v>565</v>
       </c>
@@ -11682,7 +11681,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="391" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="4:6">
       <c r="D391" t="s">
         <v>566</v>
       </c>
@@ -11693,7 +11692,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="392" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="392" spans="4:6">
       <c r="D392" t="s">
         <v>567</v>
       </c>
@@ -11704,7 +11703,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="393" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="393" spans="4:6">
       <c r="D393" t="s">
         <v>568</v>
       </c>
@@ -11715,7 +11714,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="394" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="4:6">
       <c r="D394" t="s">
         <v>570</v>
       </c>
@@ -11726,7 +11725,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="395" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="4:6">
       <c r="D395" t="s">
         <v>571</v>
       </c>
@@ -11737,7 +11736,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="396" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="4:6">
       <c r="D396" t="s">
         <v>572</v>
       </c>
@@ -11748,7 +11747,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="397" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="4:6">
       <c r="D397" t="s">
         <v>573</v>
       </c>
@@ -11759,7 +11758,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="398" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="4:6">
       <c r="D398" t="s">
         <v>574</v>
       </c>
@@ -11770,7 +11769,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="399" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="4:6">
       <c r="D399" t="s">
         <v>575</v>
       </c>
@@ -11781,7 +11780,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="400" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="4:6">
       <c r="D400" t="s">
         <v>576</v>
       </c>
@@ -11792,7 +11791,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="401" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="4:6">
       <c r="D401" t="s">
         <v>577</v>
       </c>
@@ -11803,7 +11802,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="402" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="4:6">
       <c r="D402" t="s">
         <v>578</v>
       </c>
@@ -11814,7 +11813,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="403" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="4:6">
       <c r="D403" t="s">
         <v>571</v>
       </c>
@@ -11825,7 +11824,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="404" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="4:6">
       <c r="D404" t="s">
         <v>572</v>
       </c>
@@ -11836,7 +11835,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="405" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="4:6">
       <c r="D405" t="s">
         <v>573</v>
       </c>
@@ -11847,7 +11846,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="406" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="4:6">
       <c r="D406" t="s">
         <v>574</v>
       </c>
@@ -11858,7 +11857,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="407" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="407" spans="4:6">
       <c r="D407" t="s">
         <v>575</v>
       </c>
@@ -11869,7 +11868,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="408" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="4:6">
       <c r="D408" t="s">
         <v>576</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="409" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="4:6">
       <c r="D409" t="s">
         <v>577</v>
       </c>
@@ -11891,7 +11890,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="410" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="4:6">
       <c r="D410" t="s">
         <v>579</v>
       </c>
@@ -11902,7 +11901,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="411" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="4:6">
       <c r="D411" t="s">
         <v>580</v>
       </c>
@@ -11913,7 +11912,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="412" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="4:6">
       <c r="D412" t="s">
         <v>581</v>
       </c>
@@ -11924,7 +11923,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="413" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="4:6">
       <c r="D413" t="s">
         <v>582</v>
       </c>
@@ -11935,7 +11934,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="414" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="4:6">
       <c r="D414" t="s">
         <v>583</v>
       </c>
@@ -11946,7 +11945,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="415" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="4:6">
       <c r="D415" t="s">
         <v>584</v>
       </c>
@@ -11957,7 +11956,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="416" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="4:6">
       <c r="D416" t="s">
         <v>585</v>
       </c>
@@ -11968,7 +11967,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="417" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="4:6">
       <c r="D417" t="s">
         <v>586</v>
       </c>
@@ -11979,7 +11978,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="418" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="4:6">
       <c r="D418" t="s">
         <v>587</v>
       </c>
@@ -11990,7 +11989,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="419" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="4:6">
       <c r="D419" t="s">
         <v>588</v>
       </c>
@@ -12001,7 +12000,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="420" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="4:6">
       <c r="D420" t="s">
         <v>589</v>
       </c>
@@ -12012,7 +12011,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="421" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="4:6">
       <c r="D421" t="s">
         <v>590</v>
       </c>
@@ -12023,7 +12022,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="422" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="4:6">
       <c r="D422" t="s">
         <v>591</v>
       </c>
@@ -12034,7 +12033,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="423" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="4:6">
       <c r="D423" t="s">
         <v>592</v>
       </c>
@@ -12045,7 +12044,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="424" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="4:6">
       <c r="D424" t="s">
         <v>593</v>
       </c>
@@ -12056,7 +12055,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="425" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="4:6">
       <c r="D425" t="s">
         <v>594</v>
       </c>
@@ -12067,7 +12066,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="426" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="4:6">
       <c r="D426" t="s">
         <v>595</v>
       </c>
@@ -12078,7 +12077,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="427" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="4:6">
       <c r="D427" t="s">
         <v>596</v>
       </c>
@@ -12089,7 +12088,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="428" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="4:6">
       <c r="D428" t="s">
         <v>597</v>
       </c>
@@ -12100,7 +12099,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="429" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="4:6">
       <c r="D429" t="s">
         <v>598</v>
       </c>
@@ -12111,7 +12110,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="430" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="4:6">
       <c r="D430" t="s">
         <v>599</v>
       </c>
@@ -12122,7 +12121,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="431" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="4:6">
       <c r="D431" t="s">
         <v>600</v>
       </c>
@@ -12133,7 +12132,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="432" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="4:6">
       <c r="D432" t="s">
         <v>601</v>
       </c>
@@ -12144,7 +12143,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="433" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="4:6">
       <c r="D433" t="s">
         <v>602</v>
       </c>
@@ -12155,7 +12154,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="434" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="4:6">
       <c r="D434" t="s">
         <v>603</v>
       </c>
@@ -12166,7 +12165,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="435" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="4:6">
       <c r="D435" t="s">
         <v>604</v>
       </c>
@@ -12177,7 +12176,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="436" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="4:6">
       <c r="D436" t="s">
         <v>605</v>
       </c>
@@ -12188,7 +12187,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="437" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="4:6">
       <c r="D437" t="s">
         <v>606</v>
       </c>
@@ -12199,7 +12198,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="438" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="4:6">
       <c r="D438" t="s">
         <v>607</v>
       </c>
@@ -12210,7 +12209,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="439" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="4:6">
       <c r="D439" t="s">
         <v>608</v>
       </c>
@@ -12221,7 +12220,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="440" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="4:6">
       <c r="D440" t="s">
         <v>609</v>
       </c>
@@ -12232,7 +12231,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="441" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="4:6">
       <c r="D441" t="s">
         <v>610</v>
       </c>
@@ -12243,7 +12242,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="442" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="4:6">
       <c r="D442" t="s">
         <v>611</v>
       </c>
@@ -12254,7 +12253,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="443" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="4:6">
       <c r="D443" t="s">
         <v>612</v>
       </c>
@@ -12265,7 +12264,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="444" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="4:6">
       <c r="D444" t="s">
         <v>613</v>
       </c>
@@ -12276,7 +12275,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="445" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="4:6">
       <c r="D445" t="s">
         <v>614</v>
       </c>
@@ -12287,7 +12286,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="446" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="4:6">
       <c r="D446" t="s">
         <v>615</v>
       </c>
@@ -12298,7 +12297,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="447" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="4:6">
       <c r="D447" t="s">
         <v>616</v>
       </c>
@@ -12309,7 +12308,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="448" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="448" spans="4:6">
       <c r="D448" t="s">
         <v>617</v>
       </c>
@@ -12320,7 +12319,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="449" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="4:6">
       <c r="D449" t="s">
         <v>618</v>
       </c>
@@ -12331,7 +12330,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="450" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="4:6">
       <c r="D450" t="s">
         <v>619</v>
       </c>
@@ -12342,7 +12341,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="451" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="4:6">
       <c r="D451" t="s">
         <v>612</v>
       </c>
@@ -12353,7 +12352,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="452" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="4:6">
       <c r="D452" t="s">
         <v>613</v>
       </c>
@@ -12364,7 +12363,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="453" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="4:6">
       <c r="D453" t="s">
         <v>614</v>
       </c>
@@ -12375,7 +12374,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="454" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="4:6">
       <c r="D454" t="s">
         <v>615</v>
       </c>
@@ -12386,7 +12385,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="455" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="4:6">
       <c r="D455" t="s">
         <v>616</v>
       </c>
@@ -12397,7 +12396,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="456" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="4:6">
       <c r="D456" t="s">
         <v>617</v>
       </c>
@@ -12408,7 +12407,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="457" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="4:6">
       <c r="D457" t="s">
         <v>618</v>
       </c>
@@ -12419,7 +12418,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="458" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="4:6">
       <c r="D458" t="s">
         <v>620</v>
       </c>
@@ -12430,7 +12429,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="459" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="4:6">
       <c r="D459" t="s">
         <v>621</v>
       </c>
@@ -12441,7 +12440,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="460" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="4:6">
       <c r="D460" t="s">
         <v>622</v>
       </c>
@@ -12452,7 +12451,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="461" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="4:6">
       <c r="D461" t="s">
         <v>623</v>
       </c>
@@ -12463,7 +12462,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="462" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="4:6">
       <c r="D462" t="s">
         <v>624</v>
       </c>
@@ -12474,7 +12473,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="463" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="4:6">
       <c r="D463" t="s">
         <v>625</v>
       </c>
@@ -12485,7 +12484,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="464" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="4:6">
       <c r="D464" t="s">
         <v>626</v>
       </c>
@@ -12496,7 +12495,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="465" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="465" spans="4:6">
       <c r="D465" t="s">
         <v>627</v>
       </c>
@@ -12507,7 +12506,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="466" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="4:6">
       <c r="D466" t="s">
         <v>634</v>
       </c>
@@ -12518,7 +12517,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="467" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="4:6">
       <c r="D467" t="s">
         <v>628</v>
       </c>
@@ -12529,7 +12528,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="468" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="4:6">
       <c r="D468" t="s">
         <v>635</v>
       </c>
@@ -12540,7 +12539,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="469" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="4:6">
       <c r="D469" t="s">
         <v>629</v>
       </c>
@@ -12551,7 +12550,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="470" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="4:6">
       <c r="D470" t="s">
         <v>630</v>
       </c>
@@ -12562,7 +12561,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="471" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="4:6">
       <c r="D471" t="s">
         <v>631</v>
       </c>
@@ -12573,7 +12572,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="472" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="472" spans="4:6">
       <c r="D472" t="s">
         <v>632</v>
       </c>
@@ -12584,7 +12583,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="473" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="4:6">
       <c r="D473" t="s">
         <v>633</v>
       </c>
@@ -12595,7 +12594,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="474" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="4:6">
       <c r="D474" t="s">
         <v>636</v>
       </c>
@@ -12606,7 +12605,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="475" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="4:6">
       <c r="D475" t="s">
         <v>637</v>
       </c>
@@ -12617,7 +12616,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="476" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="4:6">
       <c r="D476" t="s">
         <v>638</v>
       </c>
@@ -12628,7 +12627,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="477" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="4:6">
       <c r="D477" t="s">
         <v>639</v>
       </c>
@@ -12639,7 +12638,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="478" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="478" spans="4:6">
       <c r="D478" t="s">
         <v>640</v>
       </c>
@@ -12650,7 +12649,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="479" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="479" spans="4:6">
       <c r="D479" t="s">
         <v>641</v>
       </c>
@@ -12661,7 +12660,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="480" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="4:6">
       <c r="D480" t="s">
         <v>642</v>
       </c>
@@ -12672,7 +12671,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="481" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="481" spans="4:6">
       <c r="D481" t="s">
         <v>643</v>
       </c>
@@ -12683,7 +12682,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="482" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="482" spans="4:6">
       <c r="D482" t="s">
         <v>644</v>
       </c>
@@ -12694,7 +12693,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="483" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="483" spans="4:6">
       <c r="D483" t="s">
         <v>637</v>
       </c>
@@ -12705,7 +12704,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="484" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="484" spans="4:6">
       <c r="D484" t="s">
         <v>638</v>
       </c>
@@ -12716,7 +12715,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="485" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="485" spans="4:6">
       <c r="D485" t="s">
         <v>639</v>
       </c>
@@ -12727,7 +12726,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="486" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="486" spans="4:6">
       <c r="D486" t="s">
         <v>640</v>
       </c>
@@ -12738,7 +12737,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="487" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="487" spans="4:6">
       <c r="D487" t="s">
         <v>641</v>
       </c>
@@ -12749,7 +12748,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="488" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="488" spans="4:6">
       <c r="D488" t="s">
         <v>642</v>
       </c>
@@ -12760,7 +12759,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="489" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="489" spans="4:6">
       <c r="D489" t="s">
         <v>643</v>
       </c>
@@ -12771,7 +12770,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="490" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="490" spans="4:6">
       <c r="D490" t="s">
         <v>645</v>
       </c>
@@ -12782,7 +12781,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="491" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="491" spans="4:6">
       <c r="D491" t="s">
         <v>646</v>
       </c>
@@ -12793,7 +12792,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="492" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="492" spans="4:6">
       <c r="D492" t="s">
         <v>647</v>
       </c>
@@ -12804,7 +12803,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="493" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="493" spans="4:6">
       <c r="D493" t="s">
         <v>648</v>
       </c>
@@ -12815,7 +12814,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="494" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="494" spans="4:6">
       <c r="D494" t="s">
         <v>649</v>
       </c>
@@ -12826,7 +12825,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="495" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="495" spans="4:6">
       <c r="D495" t="s">
         <v>650</v>
       </c>
@@ -12837,7 +12836,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="496" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="496" spans="4:6">
       <c r="D496" t="s">
         <v>651</v>
       </c>
@@ -12848,7 +12847,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="497" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="497" spans="4:6">
       <c r="D497" t="s">
         <v>652</v>
       </c>
@@ -12859,7 +12858,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="498" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="498" spans="4:6">
       <c r="D498" t="s">
         <v>653</v>
       </c>
@@ -12870,7 +12869,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="499" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="499" spans="4:6">
       <c r="D499" t="s">
         <v>654</v>
       </c>
@@ -12881,7 +12880,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="500" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="500" spans="4:6">
       <c r="D500" t="s">
         <v>655</v>
       </c>
@@ -12892,7 +12891,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="501" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="501" spans="4:6">
       <c r="D501" t="s">
         <v>656</v>
       </c>
@@ -12903,7 +12902,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="502" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="502" spans="4:6">
       <c r="D502" t="s">
         <v>657</v>
       </c>
@@ -12914,7 +12913,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="503" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="503" spans="4:6">
       <c r="D503" t="s">
         <v>658</v>
       </c>
@@ -12925,7 +12924,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="504" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="504" spans="4:6">
       <c r="D504" t="s">
         <v>659</v>
       </c>
@@ -12936,7 +12935,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="505" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="505" spans="4:6">
       <c r="D505" t="s">
         <v>660</v>
       </c>
@@ -12947,7 +12946,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="506" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="506" spans="4:6">
       <c r="D506" t="s">
         <v>661</v>
       </c>
@@ -12958,7 +12957,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="507" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="507" spans="4:6">
       <c r="D507" t="s">
         <v>662</v>
       </c>
@@ -12969,7 +12968,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="508" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="508" spans="4:6">
       <c r="D508" t="s">
         <v>663</v>
       </c>
@@ -12980,7 +12979,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="509" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="509" spans="4:6">
       <c r="D509" t="s">
         <v>664</v>
       </c>
@@ -12991,7 +12990,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="510" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="510" spans="4:6">
       <c r="D510" t="s">
         <v>665</v>
       </c>
@@ -13002,7 +13001,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="511" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="511" spans="4:6">
       <c r="D511" t="s">
         <v>666</v>
       </c>
@@ -13013,7 +13012,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="512" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="512" spans="4:6">
       <c r="D512" t="s">
         <v>667</v>
       </c>
@@ -13024,7 +13023,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="513" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="4:6">
       <c r="D513" t="s">
         <v>668</v>
       </c>
@@ -13035,7 +13034,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="514" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="4:6">
       <c r="D514" t="s">
         <v>669</v>
       </c>
@@ -13046,7 +13045,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="515" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="515" spans="4:6">
       <c r="D515" t="s">
         <v>670</v>
       </c>
@@ -13057,7 +13056,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="516" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="4:6">
       <c r="D516" t="s">
         <v>671</v>
       </c>
@@ -13068,7 +13067,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="517" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="4:6">
       <c r="D517" t="s">
         <v>672</v>
       </c>
@@ -13079,7 +13078,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="518" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="4:6">
       <c r="D518" t="s">
         <v>673</v>
       </c>
@@ -13090,7 +13089,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="519" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="4:6">
       <c r="D519" t="s">
         <v>674</v>
       </c>
@@ -13101,7 +13100,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="520" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="4:6">
       <c r="D520" t="s">
         <v>675</v>
       </c>
@@ -13112,7 +13111,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="521" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="4:6">
       <c r="D521" t="s">
         <v>676</v>
       </c>
@@ -13123,7 +13122,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="522" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="4:6">
       <c r="D522" t="s">
         <v>677</v>
       </c>
@@ -13134,7 +13133,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="523" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="4:6">
       <c r="D523" t="s">
         <v>678</v>
       </c>
@@ -13145,7 +13144,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="524" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="4:6">
       <c r="D524" t="s">
         <v>679</v>
       </c>
@@ -13156,7 +13155,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="525" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="4:6">
       <c r="D525" t="s">
         <v>680</v>
       </c>
@@ -13167,7 +13166,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="526" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="4:6">
       <c r="D526" t="s">
         <v>681</v>
       </c>
@@ -13178,7 +13177,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="527" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="4:6">
       <c r="D527" t="s">
         <v>682</v>
       </c>
@@ -13189,7 +13188,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="528" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="4:6">
       <c r="D528" t="s">
         <v>683</v>
       </c>
@@ -13200,7 +13199,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="529" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="529" spans="4:6">
       <c r="D529" t="s">
         <v>684</v>
       </c>
